--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484678_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484678_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9438</v>
+        <v>7.3893</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1408</v>
+        <v>3.3882</v>
       </c>
       <c r="F2" t="n">
-        <v>3.803</v>
+        <v>4.0012</v>
       </c>
       <c r="G2" t="n">
         <v>5.0048</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1605</v>
+        <v>0.2851</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3499</v>
+        <v>-0.1025</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1894</v>
+        <v>0.3876</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8436</v>
+        <v>6.8595</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2773</v>
+        <v>2.5658</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5663</v>
+        <v>4.2937</v>
       </c>
       <c r="G3" t="n">
         <v>5.7197</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3334</v>
+        <v>0.3493</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4955</v>
+        <v>-0.207</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8289</v>
+        <v>0.5563</v>
       </c>
       <c r="V3" t="n">
         <v>1.89</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9519</v>
+        <v>5.4422</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1908</v>
+        <v>4.7024</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7611</v>
+        <v>0.7398</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8475</v>
+        <v>3.7172</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1905</v>
+        <v>2.7813</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6569</v>
+        <v>0.9359</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4313</v>
+        <v>4.2244</v>
       </c>
       <c r="K4" t="n">
-        <v>1.864</v>
+        <v>2.1983</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4327</v>
+        <v>2.0261</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4161</v>
+        <v>-0.5072</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3265</v>
+        <v>0.583</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0896</v>
+        <v>-1.0902</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1991</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5101</v>
+        <v>-0.4894</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0423</v>
+        <v>-0.2259</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4678</v>
+        <v>-0.2636</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3115</v>
+        <v>1.2982</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6335</v>
+        <v>1.6202</v>
       </c>
       <c r="X4" t="n">
         <v>-0.3219</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8678</v>
+        <v>5.0024</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6728</v>
+        <v>3.8074</v>
       </c>
       <c r="F5" t="n">
         <v>1.195</v>
@@ -844,10 +844,10 @@
         <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9427</v>
+        <v>1.0773</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2074</v>
+        <v>0.342</v>
       </c>
       <c r="U5" t="n">
         <v>0.7353</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3787</v>
+        <v>4.699</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6885</v>
+        <v>1.0369</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6902</v>
+        <v>3.662</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7172</v>
+        <v>2.8475</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7813</v>
+        <v>2.1905</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9359</v>
+        <v>0.6569</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2244</v>
+        <v>1.4313</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1983</v>
+        <v>1.864</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0261</v>
+        <v>-0.4327</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5072</v>
+        <v>1.4161</v>
       </c>
       <c r="N6" t="n">
-        <v>0.583</v>
+        <v>0.3265</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0902</v>
+        <v>1.0896</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.2572</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2398</v>
+        <v>-0.1116</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3131</v>
+        <v>0.3688</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2982</v>
+        <v>0.3115</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6202</v>
+        <v>0.6335</v>
       </c>
       <c r="X6" t="n">
         <v>-0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.9901</v>
+        <v>3.5615</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4698</v>
+        <v>-0.7994</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4599</v>
+        <v>4.3608</v>
       </c>
       <c r="G7" t="n">
         <v>5.3457</v>
@@ -1000,13 +1000,13 @@
         <v>2.5656</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6315</v>
+        <v>0.2029</v>
       </c>
       <c r="T7" t="n">
-        <v>0.181</v>
+        <v>-0.1485</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4505</v>
+        <v>0.3514</v>
       </c>
       <c r="V7" t="n">
         <v>0.945</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7314</v>
+        <v>2.5016</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0012</v>
+        <v>1.3997</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7302</v>
+        <v>1.1018</v>
       </c>
       <c r="G8" t="n">
         <v>1.0466</v>
@@ -1078,13 +1078,13 @@
         <v>1.0995</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.017</v>
+        <v>-0.2468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8808</v>
+        <v>-0.4823</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1361</v>
+        <v>0.2355</v>
       </c>
       <c r="V8" t="n">
         <v>0.6022999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. CAMPOS MONTEIRO</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2115</v>
+        <v>-0.8534</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1209</v>
+        <v>0.4435</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9094</v>
+        <v>-1.2969</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4152</v>
+        <v>-0.9905</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4826</v>
+        <v>0.3593</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0674</v>
+        <v>-1.3498</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7906</v>
+        <v>1.3194</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.217</v>
+        <v>-0.0558</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5736</v>
+        <v>1.3753</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3754</v>
+        <v>-2.31</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2656</v>
+        <v>0.4151</v>
       </c>
       <c r="O10" t="n">
-        <v>0.641</v>
+        <v>-2.725</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7126</v>
+        <v>0.2758</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3303</v>
+        <v>0.0404</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3823</v>
+        <v>0.2355</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ROMERA GALINDO</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2511</v>
+        <v>-0.963</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3839</v>
+        <v>-0.553</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1328</v>
+        <v>-0.41</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2676</v>
+        <v>-2.8582</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0528</v>
+        <v>1.6487</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2147</v>
+        <v>-4.5069</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2187</v>
+        <v>-0.9161</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6194</v>
+        <v>1.5389</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5994</v>
+        <v>-2.455</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0489</v>
+        <v>-1.9421</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4335</v>
+        <v>0.1098</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3846</v>
+        <v>-2.0519</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5333</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1652</v>
+        <v>0.0125</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3681</v>
+        <v>0.4875</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5785</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>E. CAMPOS MONTEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3204</v>
+        <v>-1.044</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1474</v>
+        <v>-1.9286</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.173</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9905</v>
+        <v>-1.4152</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3593</v>
+        <v>-1.4826</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3498</v>
+        <v>0.0674</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3194</v>
+        <v>-1.7906</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0558</v>
+        <v>-1.217</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3753</v>
+        <v>-0.5736</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.31</v>
+        <v>0.3754</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4151</v>
+        <v>-0.2656</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.725</v>
+        <v>0.641</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1912</v>
+        <v>-0.5451</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5505</v>
+        <v>-0.138</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3593</v>
+        <v>-0.4071</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>J. ROMERA GALINDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8948</v>
+        <v>-1.1301</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3362</v>
+        <v>-1.2877</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5586</v>
+        <v>0.1576</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8582</v>
+        <v>-1.2676</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6487</v>
+        <v>-1.0528</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.5069</v>
+        <v>-0.2147</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9161</v>
+        <v>-1.2187</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5389</v>
+        <v>-0.6194</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.455</v>
+        <v>-0.5994</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9421</v>
+        <v>-0.0489</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1098</v>
+        <v>-0.4335</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0519</v>
+        <v>0.3846</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1833</v>
+        <v>0.5498</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4318</v>
+        <v>-0.4123</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3389</v>
+        <v>-0.3433</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5785</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.4652</v>
+        <v>-2.3501</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6217</v>
+        <v>-1.3333</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8435</v>
+        <v>-1.0169</v>
       </c>
       <c r="G14" t="n">
         <v>-2.6988</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1053</v>
+        <v>0.2204</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2202</v>
+        <v>0.0683</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3256</v>
+        <v>0.1521</v>
       </c>
       <c r="V14" t="n">
         <v>0.3115</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>29.5145</v>
+        <v>30.0651</v>
       </c>
       <c r="E15" t="n">
-        <v>11.8417</v>
+        <v>12.3921</v>
       </c>
       <c r="F15" t="n">
-        <v>17.6728</v>
+        <v>17.6727</v>
       </c>
       <c r="G15" t="n">
         <v>19.1774</v>
@@ -1594,7 +1594,7 @@
         <v>18.3773</v>
       </c>
       <c r="I15" t="n">
-        <v>0.800099999999998</v>
+        <v>0.8000999999999994</v>
       </c>
       <c r="J15" t="n">
         <v>21.3266</v>
@@ -1606,7 +1606,7 @@
         <v>6.4131</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.149399999999999</v>
+        <v>-2.1494</v>
       </c>
       <c r="N15" t="n">
         <v>3.4638</v>
@@ -1624,13 +1624,13 @@
         <v>17.4093</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9236999999999993</v>
+        <v>1.4744</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5722</v>
+        <v>-1.0216</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4961</v>
+        <v>2.496</v>
       </c>
       <c r="V15" t="n">
         <v>7.581</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ANTONI RODRIGUEZ</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6114</v>
+        <v>0.755</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1985</v>
+        <v>1.5759</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5871</v>
+        <v>-0.8209</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1231</v>
+        <v>-0.9876</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2779</v>
+        <v>-3.4785</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4011</v>
+        <v>2.4909</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9643</v>
+        <v>1.029</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.437</v>
+        <v>-1.8147</v>
       </c>
       <c r="L16" t="n">
-        <v>3.4014</v>
+        <v>2.8437</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8412</v>
+        <v>-2.0166</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8409</v>
+        <v>-1.6638</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0003</v>
+        <v>-0.3528</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5799</v>
+        <v>-0.8071</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7082</v>
+        <v>-0.4189</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1283</v>
+        <v>-0.3882</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1912</v>
+        <v>1.267</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.5577</v>
+        <v>0.9658</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6335</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>M. ANTONI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2469</v>
+        <v>-0.2869</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3131</v>
+        <v>0.2755</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.5624</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7275</v>
+        <v>0.1231</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6505</v>
+        <v>-3.2779</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.077</v>
+        <v>3.4011</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4295</v>
+        <v>1.9643</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5445</v>
+        <v>-1.437</v>
       </c>
       <c r="L18" t="n">
-        <v>0.885</v>
+        <v>3.4014</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.157</v>
+        <v>-1.8412</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.195</v>
+        <v>-1.8409</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.962</v>
+        <v>-0.0003</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9321</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3823</v>
+        <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2364</v>
+        <v>0.6816</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5279</v>
+        <v>0.7851</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7085</v>
+        <v>-0.1035</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2878</v>
+        <v>-2.1912</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2878</v>
+        <v>-1.5577</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0018</v>
+        <v>-0.7977</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0952</v>
+        <v>-0.3599</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0934</v>
+        <v>-0.4378</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9876</v>
+        <v>-1.7275</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.4785</v>
+        <v>-1.6505</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4909</v>
+        <v>-0.077</v>
       </c>
       <c r="J19" t="n">
-        <v>1.029</v>
+        <v>1.4295</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8147</v>
+        <v>0.5445</v>
       </c>
       <c r="L19" t="n">
-        <v>2.8437</v>
+        <v>0.885</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0166</v>
+        <v>-3.157</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6638</v>
+        <v>-2.195</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3528</v>
+        <v>-0.962</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5604</v>
+        <v>0.1917</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.1451</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6607</v>
+        <v>0.3369</v>
       </c>
       <c r="V19" t="n">
-        <v>1.267</v>
+        <v>1.2878</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9658</v>
+        <v>1.2878</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7436</v>
+        <v>-1.7849</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9845</v>
+        <v>-0.1691</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2409</v>
+        <v>-1.6158</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6812</v>
+        <v>-0.9739</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4794</v>
+        <v>-2.3911</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7982</v>
+        <v>1.4172</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1799</v>
+        <v>1.0748</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5543</v>
+        <v>-1.1119</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7342</v>
+        <v>2.1868</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8611</v>
+        <v>-2.0487</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.925</v>
+        <v>-1.2792</v>
       </c>
       <c r="O20" t="n">
-        <v>0.064</v>
+        <v>-0.7695</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07630000000000001</v>
+        <v>-0.2117</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3318</v>
+        <v>-0.3276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4081</v>
+        <v>0.1159</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9554</v>
+        <v>-0.9658</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9554</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6062</v>
+        <v>-1.7931</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9863</v>
+        <v>-1.9845</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5925</v>
+        <v>0.1914</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7195</v>
+        <v>-0.6812</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4284</v>
+        <v>-1.4794</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2911</v>
+        <v>0.7982</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6742</v>
+        <v>0.1799</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4522</v>
+        <v>-0.5543</v>
       </c>
       <c r="L21" t="n">
-        <v>0.222</v>
+        <v>0.7342</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3937</v>
+        <v>-0.8611</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8805</v>
+        <v>-0.925</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5131</v>
+        <v>0.064</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2828</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6355</v>
+        <v>0.0268</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0098</v>
+        <v>-0.3318</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3743</v>
+        <v>0.3586</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5339</v>
+        <v>-0.9554</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8559</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8733</v>
+        <v>-2.0628</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0345</v>
+        <v>1.8517</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8388</v>
+        <v>-3.9146</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9739</v>
+        <v>-0.7195</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3911</v>
+        <v>-0.4284</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4172</v>
+        <v>-0.2911</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0748</v>
+        <v>1.6742</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1119</v>
+        <v>1.4522</v>
       </c>
       <c r="L22" t="n">
-        <v>2.1868</v>
+        <v>0.222</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0487</v>
+        <v>-2.3937</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2792</v>
+        <v>-1.8805</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7695</v>
+        <v>-0.5131</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3001</v>
+        <v>-0.0922</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.193</v>
+        <v>-0.1444</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.107</v>
+        <v>0.0522</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9658</v>
+        <v>-2.5339</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9658</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2641</v>
+        <v>-4.2889</v>
       </c>
       <c r="E23" t="n">
         <v>-2.5105</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7536</v>
+        <v>-1.7784</v>
       </c>
       <c r="G23" t="n">
         <v>-3.8802</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2392</v>
+        <v>0.2144</v>
       </c>
       <c r="T23" t="n">
         <v>-0.0935</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3326</v>
+        <v>0.3079</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6231</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7838</v>
+        <v>-4.5172</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4369</v>
+        <v>-3.2446</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3469</v>
+        <v>-1.2726</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1365</v>
@@ -2326,13 +2326,13 @@
         <v>1.6493</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0138</v>
+        <v>-0.7472</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9728</v>
+        <v>-0.7805</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.041</v>
+        <v>0.0334</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8926</v>
+        <v>-6.4555</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5856</v>
+        <v>-4.2971</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.307</v>
+        <v>-2.1584</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6034</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6166</v>
+        <v>-0.1795</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7896</v>
+        <v>-0.5011</v>
       </c>
       <c r="U25" t="n">
-        <v>0.173</v>
+        <v>0.3216</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5889</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.8363</v>
+        <v>-8.9077</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.3392</v>
+        <v>-9.4354</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5029</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2157</v>
@@ -2482,13 +2482,13 @@
         <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0708</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4419</v>
+        <v>-0.5381</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5127</v>
+        <v>0.5375</v>
       </c>
       <c r="V26" t="n">
         <v>-0.0104</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-29.5147</v>
+        <v>-29.5146</v>
       </c>
       <c r="E27" t="n">
-        <v>-17.673</v>
+        <v>-17.6729</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.8417</v>
+        <v>-11.8418</v>
       </c>
       <c r="G27" t="n">
         <v>-19.1773</v>
@@ -2530,10 +2530,10 @@
         <v>-18.377</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8000999999999996</v>
+        <v>-0.8001000000000014</v>
       </c>
       <c r="J27" t="n">
-        <v>2.1492</v>
+        <v>2.149199999999999</v>
       </c>
       <c r="K27" t="n">
         <v>-3.4637</v>
@@ -2548,7 +2548,7 @@
         <v>-14.9132</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.413099999999999</v>
+        <v>-6.4131</v>
       </c>
       <c r="P27" t="n">
         <v>-1.8327</v>
@@ -2560,16 +2560,16 @@
         <v>15.5767</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.9238000000000004</v>
+        <v>-0.9238000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.496</v>
+        <v>-2.4959</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5722</v>
+        <v>1.5723</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.580899999999998</v>
+        <v>-7.5809</v>
       </c>
       <c r="W27" t="n">
         <v>0.0832</v>
